--- a/3th course/МИЭП/лаба 3.xlsx
+++ b/3th course/МИЭП/лаба 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antonkorolev/Documents/university/3th course/МИЭП/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505AC0DE-59BA-0944-B646-9DDC4A0F3E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5EACC6-DE24-9A4E-A769-C07221233092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{25120A0A-33C2-3843-87D5-659787C98955}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16880" xr2:uid="{25120A0A-33C2-3843-87D5-659787C98955}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
@@ -338,6 +338,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -346,12 +352,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2019,7 +2019,7 @@
       <c r="H2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="15">
+      <c r="I2" s="12">
         <f>ABS(D2/B2*100)</f>
         <v>0.83951111111111409</v>
       </c>
@@ -2073,7 +2073,7 @@
         <f>$D3*$D2</f>
         <v>-0.46844720000000512</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="12">
         <f t="shared" ref="I3:I10" si="3">ABS(D3/B3*100)</f>
         <v>0.71264367816092478</v>
       </c>
@@ -2122,7 +2122,7 @@
         <f t="shared" ref="H4:H10" si="7">$D4*$D3</f>
         <v>0.62620000000000775</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="12">
         <f t="shared" si="3"/>
         <v>1.1882352941176531</v>
       </c>
@@ -2171,7 +2171,7 @@
         <f t="shared" si="7"/>
         <v>-1.6261000000000077</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="12">
         <f t="shared" si="3"/>
         <v>1.8720930232558133</v>
       </c>
@@ -2220,7 +2220,7 @@
         <f t="shared" si="7"/>
         <v>-1.2396999999999931</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="12">
         <f t="shared" si="3"/>
         <v>0.9390243902438975</v>
       </c>
@@ -2269,7 +2269,7 @@
         <f t="shared" si="7"/>
         <v>0.89319999999999278</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="12">
         <f t="shared" si="3"/>
         <v>1.4499999999999957</v>
       </c>
@@ -2318,7 +2318,7 @@
         <f t="shared" si="7"/>
         <v>-1.6935999999999878</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="12">
         <f t="shared" si="3"/>
         <v>1.8024691358024616</v>
       </c>
@@ -2367,7 +2367,7 @@
         <f t="shared" si="7"/>
         <v>0.116799999999997</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="12">
         <f t="shared" si="3"/>
         <v>0.10256410256410037</v>
       </c>
@@ -2416,7 +2416,7 @@
         <f t="shared" si="7"/>
         <v>-2.4799999999999652E-2</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="12">
         <f t="shared" si="3"/>
         <v>0.4078947368421082</v>
       </c>
@@ -2463,10 +2463,10 @@
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
-      <c r="O13" s="13" t="s">
+      <c r="O13" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="P13" s="14"/>
+      <c r="P13" s="16"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="9"/>
@@ -2496,11 +2496,11 @@
       </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
       <c r="D15" s="9"/>
       <c r="F15" t="s">
         <v>9</v>
@@ -2529,9 +2529,9 @@
       </c>
     </row>
     <row r="16" spans="1:16" ht="16" customHeight="1">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
       <c r="D16" s="9"/>
       <c r="K16" s="2">
         <v>10</v>
@@ -2558,12 +2558,12 @@
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
       <c r="K17" s="2">
         <v>11</v>
       </c>
@@ -2585,10 +2585,10 @@
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
     </row>
     <row r="19" spans="1:17">
       <c r="D19" t="s">
@@ -2598,10 +2598,10 @@
         <f>(MAX(D2:D10) - MIN(D2:D10))/ STDEV(D2:D10)</f>
         <v>2.6501519480021876</v>
       </c>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
     </row>
     <row r="20" spans="1:17">
       <c r="D20" t="s">
@@ -2632,7 +2632,7 @@
       <c r="N24" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
-      <c r="O24" s="16">
+      <c r="O24" s="13">
         <f>ABS(H11/E11)</f>
         <v>0.39089467737428008</v>
       </c>
